--- a/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0001T0006Z000C1N21_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0001T0006Z000C1N21_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>9.243420519511384</v>
+        <v>1.5020558344206</v>
       </c>
       <c r="D2" t="n">
-        <v>9.091813114037265</v>
+        <v>1.477419631031056</v>
       </c>
       <c r="E2" t="n">
-        <v>19.51140884292002</v>
+        <v>3.170603936974503</v>
       </c>
       <c r="F2" t="n">
-        <v>19.54630318331809</v>
+        <v>3.176274267289191</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>27.12262468715959</v>
+        <v>4.407426511663433</v>
       </c>
       <c r="D3" t="n">
-        <v>27.47055375087001</v>
+        <v>4.463964984516377</v>
       </c>
       <c r="E3" t="n">
-        <v>19.51140884292002</v>
+        <v>3.170603936974503</v>
       </c>
       <c r="F3" t="n">
-        <v>19.54630318331809</v>
+        <v>3.176274267289191</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>19.74812327072409</v>
+        <v>3.209070031492665</v>
       </c>
       <c r="D4" t="n">
-        <v>18.88764758164785</v>
+        <v>3.069242732017775</v>
       </c>
       <c r="E4" t="n">
-        <v>19.51140884292002</v>
+        <v>3.170603936974503</v>
       </c>
       <c r="F4" t="n">
-        <v>19.54630318331809</v>
+        <v>3.176274267289191</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>2.567366117986767</v>
+        <v>0.4171969941728497</v>
       </c>
       <c r="D5" t="n">
-        <v>3.803994928764171</v>
+        <v>0.6181491759241777</v>
       </c>
       <c r="E5" t="n">
-        <v>19.51140884292002</v>
+        <v>3.170603936974503</v>
       </c>
       <c r="F5" t="n">
-        <v>19.54630318331809</v>
+        <v>3.176274267289191</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>39.16641256339968</v>
+        <v>6.364542041552449</v>
       </c>
       <c r="D6" t="n">
-        <v>40.39170462791535</v>
+        <v>6.563652002036243</v>
       </c>
       <c r="E6" t="n">
-        <v>19.51140884292002</v>
+        <v>3.170603936974503</v>
       </c>
       <c r="F6" t="n">
-        <v>19.54630318331809</v>
+        <v>3.176274267289191</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>32.90311401017699</v>
+        <v>5.346756026653761</v>
       </c>
       <c r="D7" t="n">
-        <v>33.93992375762707</v>
+        <v>5.515237610614399</v>
       </c>
       <c r="E7" t="n">
-        <v>19.51140884292002</v>
+        <v>3.170603936974503</v>
       </c>
       <c r="F7" t="n">
-        <v>19.54630318331809</v>
+        <v>3.176274267289191</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>41.46146513892194</v>
+        <v>6.737488085074816</v>
       </c>
       <c r="D8" t="n">
-        <v>41.53516312388427</v>
+        <v>6.749464007631194</v>
       </c>
       <c r="E8" t="n">
-        <v>19.51140884292002</v>
+        <v>3.170603936974503</v>
       </c>
       <c r="F8" t="n">
-        <v>19.54630318331809</v>
+        <v>3.176274267289191</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>37.28435967357851</v>
+        <v>6.058708446956508</v>
       </c>
       <c r="D9" t="n">
-        <v>37.97362541687875</v>
+        <v>6.170714130242796</v>
       </c>
       <c r="E9" t="n">
-        <v>19.51140884292002</v>
+        <v>3.170603936974503</v>
       </c>
       <c r="F9" t="n">
-        <v>19.54630318331809</v>
+        <v>3.176274267289191</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>73.25123494000751</v>
+        <v>11.90332567775122</v>
       </c>
       <c r="D10" t="n">
-        <v>73.54144351887899</v>
+        <v>11.95048457181784</v>
       </c>
       <c r="E10" t="n">
-        <v>19.51140884292002</v>
+        <v>3.170603936974503</v>
       </c>
       <c r="F10" t="n">
-        <v>19.54630318331809</v>
+        <v>3.176274267289191</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
